--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/purple_dreams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD52128-8AB4-B34A-B960-D1115E70DBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BAB8A8-7D5A-D34A-B87B-B6CB1E8A629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14540" yWindow="1800" windowWidth="18680" windowHeight="17440" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
+    <workbookView xWindow="14540" yWindow="1800" windowWidth="18680" windowHeight="17440" activeTab="6" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
   <sheets>
     <sheet name="Upcoming" sheetId="6" r:id="rId1"/>
@@ -18,7 +18,9 @@
     <sheet name="Milestone" sheetId="4" r:id="rId3"/>
     <sheet name="Discography" sheetId="1" r:id="rId4"/>
     <sheet name="MusicVideo" sheetId="3" r:id="rId5"/>
-    <sheet name="Product" sheetId="2" r:id="rId6"/>
+    <sheet name="Fanbase" sheetId="7" r:id="rId6"/>
+    <sheet name="Project" sheetId="8" r:id="rId7"/>
+    <sheet name="Product" sheetId="2" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="473">
   <si>
     <t>Jungkook</t>
   </si>
@@ -1395,6 +1397,81 @@
   </si>
   <si>
     <t>Taehyung is releasing his second solo Album</t>
+  </si>
+  <si>
+    <t>fb_name</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>focus</t>
+  </si>
+  <si>
+    <t>streamfortaekook</t>
+  </si>
+  <si>
+    <t>streaming</t>
+  </si>
+  <si>
+    <t>fb for streaming</t>
+  </si>
+  <si>
+    <t>tetekoofm</t>
+  </si>
+  <si>
+    <t>stationhead</t>
+  </si>
+  <si>
+    <t>taekookuk</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>apple music</t>
+  </si>
+  <si>
+    <t>tkeurope</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Voting</t>
+  </si>
+  <si>
+    <t>fb for voting</t>
+  </si>
+  <si>
+    <t>logo</t>
+  </si>
+  <si>
+    <t>stk.jpeg</t>
+  </si>
+  <si>
+    <t>tkfm.jpeg</t>
+  </si>
+  <si>
+    <t>tkuk.jpeg</t>
+  </si>
+  <si>
+    <t>tkeu.jpeg</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>Project 1</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Project 1 trial to fill the gap in description</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1480,6 +1557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -19582,6 +19660,152 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB95BEF-80E6-B142-8CAB-761830DB341E}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D4" t="s">
+        <v>459</v>
+      </c>
+      <c r="E4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45953261-3892-AF44-BD43-F53DBB4833E1}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="10">
+        <v>45580</v>
+      </c>
+      <c r="C2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE86AF9-D9C6-C14D-B882-6BAE66AC5796}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BAB8A8-7D5A-D34A-B87B-B6CB1E8A629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBA55CD-2FFD-3448-80D7-5108545FF837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14540" yWindow="1800" windowWidth="18680" windowHeight="17440" activeTab="6" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
+    <workbookView xWindow="14540" yWindow="1800" windowWidth="18680" windowHeight="17440" activeTab="3" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
   <sheets>
     <sheet name="Upcoming" sheetId="6" r:id="rId1"/>
     <sheet name="Memory" sheetId="5" r:id="rId2"/>
     <sheet name="Milestone" sheetId="4" r:id="rId3"/>
-    <sheet name="Discography" sheetId="1" r:id="rId4"/>
-    <sheet name="MusicVideo" sheetId="3" r:id="rId5"/>
-    <sheet name="Fanbase" sheetId="7" r:id="rId6"/>
-    <sheet name="Project" sheetId="8" r:id="rId7"/>
-    <sheet name="Product" sheetId="2" r:id="rId8"/>
+    <sheet name="Radio" sheetId="9" r:id="rId4"/>
+    <sheet name="Discography" sheetId="1" r:id="rId5"/>
+    <sheet name="MusicVideo" sheetId="3" r:id="rId6"/>
+    <sheet name="Fanbase" sheetId="7" r:id="rId7"/>
+    <sheet name="Project" sheetId="8" r:id="rId8"/>
+    <sheet name="Product" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="492">
   <si>
     <t>Jungkook</t>
   </si>
@@ -1472,6 +1473,63 @@
   </si>
   <si>
     <t>Project 1 trial to fill the gap in description</t>
+  </si>
+  <si>
+    <t>station_logo</t>
+  </si>
+  <si>
+    <t>station_name</t>
+  </si>
+  <si>
+    <t>station_link</t>
+  </si>
+  <si>
+    <t>request_link</t>
+  </si>
+  <si>
+    <t>Hot106</t>
+  </si>
+  <si>
+    <t>Island106</t>
+  </si>
+  <si>
+    <t>TuckA56Radio</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>https://hot106.cgrmedia.ca/</t>
+  </si>
+  <si>
+    <t>https://island106.com/listen-live/</t>
+  </si>
+  <si>
+    <t>https://www.tucka56radio.com/</t>
+  </si>
+  <si>
+    <t>hot106.jpeg</t>
+  </si>
+  <si>
+    <t>island106.jpeg</t>
+  </si>
+  <si>
+    <t>tucka56radio.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.hits100arizona.com/request</t>
+  </si>
+  <si>
+    <t>Hits100AZ</t>
+  </si>
+  <si>
+    <t>hits100az.jpeg</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/hits-100-9797/</t>
   </si>
 </sst>
 </file>
@@ -2193,6 +2251,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2054D5E-E4FB-924C-9EF1-5CAB0A730ACC}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3C3D97-69CD-0B46-9892-9CF02B5710A8}">
   <dimension ref="A1:N931"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -17525,7 +17680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B981EFC-1AD7-EC4B-9347-256C8C05A87B}">
   <dimension ref="A1:C177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19659,7 +19814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB95BEF-80E6-B142-8CAB-761830DB341E}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19758,7 +19913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45953261-3892-AF44-BD43-F53DBB4833E1}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19805,7 +19960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE86AF9-D9C6-C14D-B882-6BAE66AC5796}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBA55CD-2FFD-3448-80D7-5108545FF837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AFFEF4-B7C4-BE46-9AFD-CCE30CEB26F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14540" yWindow="1800" windowWidth="18680" windowHeight="17440" activeTab="3" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
+    <workbookView xWindow="15020" yWindow="3080" windowWidth="22560" windowHeight="17440" activeTab="5" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
   <sheets>
     <sheet name="Upcoming" sheetId="6" r:id="rId1"/>
     <sheet name="Memory" sheetId="5" r:id="rId2"/>
     <sheet name="Milestone" sheetId="4" r:id="rId3"/>
-    <sheet name="Radio" sheetId="9" r:id="rId4"/>
-    <sheet name="Discography" sheetId="1" r:id="rId5"/>
-    <sheet name="MusicVideo" sheetId="3" r:id="rId6"/>
-    <sheet name="Fanbase" sheetId="7" r:id="rId7"/>
-    <sheet name="Project" sheetId="8" r:id="rId8"/>
+    <sheet name="Discography" sheetId="1" r:id="rId4"/>
+    <sheet name="MusicVideo" sheetId="3" r:id="rId5"/>
+    <sheet name="Fanbase" sheetId="7" r:id="rId6"/>
+    <sheet name="Project" sheetId="8" r:id="rId7"/>
+    <sheet name="Radio" sheetId="9" r:id="rId8"/>
     <sheet name="Product" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="542">
   <si>
     <t>Jungkook</t>
   </si>
@@ -1433,9 +1433,6 @@
     <t>Global</t>
   </si>
   <si>
-    <t>apple music</t>
-  </si>
-  <si>
     <t>tkeurope</t>
   </si>
   <si>
@@ -1530,6 +1527,160 @@
   </si>
   <si>
     <t>https://www.iheart.com/live/hits-100-9797/</t>
+  </si>
+  <si>
+    <t>Home of the #KPopFrenzy - A CGR Media Station 
+Available globally on the LIVE365 app &amp; http://hot106.ca. Support HOT106: https://buymeacoffee.com/hot106mast5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desc for island </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desc for tucka56 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desc for hits100az </t>
+  </si>
+  <si>
+    <t>tkasia.jpeg</t>
+  </si>
+  <si>
+    <t>tkvt.jpeg</t>
+  </si>
+  <si>
+    <t>tkus.jpeg</t>
+  </si>
+  <si>
+    <t>tkcol.jpeg</t>
+  </si>
+  <si>
+    <t>tkger.jpeg</t>
+  </si>
+  <si>
+    <t>tkhond.jpeg</t>
+  </si>
+  <si>
+    <t>tkindo.jpeg</t>
+  </si>
+  <si>
+    <t>tkjp.jpeg</t>
+  </si>
+  <si>
+    <t>tkmx.jpeg</t>
+  </si>
+  <si>
+    <t>tktt.jpeg</t>
+  </si>
+  <si>
+    <t>tkind.jpeg</t>
+  </si>
+  <si>
+    <t>taekookusa</t>
+  </si>
+  <si>
+    <t>Regional FB</t>
+  </si>
+  <si>
+    <t>Tiktok</t>
+  </si>
+  <si>
+    <t>tktiktok</t>
+  </si>
+  <si>
+    <t>tkvoting</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Columbia</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>tkasia</t>
+  </si>
+  <si>
+    <t>tkcolumbia</t>
+  </si>
+  <si>
+    <t>tkgermany</t>
+  </si>
+  <si>
+    <t>tkhonduras</t>
+  </si>
+  <si>
+    <t>tkindonesia</t>
+  </si>
+  <si>
+    <t>tkjapan</t>
+  </si>
+  <si>
+    <t>tkmexico</t>
+  </si>
+  <si>
+    <t>tkindia</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>facebook</t>
+  </si>
+  <si>
+    <t>bluesky</t>
+  </si>
+  <si>
+    <t>instagram</t>
+  </si>
+  <si>
+    <t>https://x.com/stream4taekook</t>
+  </si>
+  <si>
+    <t>https://x.com/tetekoofm</t>
+  </si>
+  <si>
+    <t>https://instagram.com/tetekoo_fm</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/tetekoofm</t>
+  </si>
+  <si>
+    <t>https://bsky.app/profile/tetekoofm.bsky.social</t>
+  </si>
+  <si>
+    <t>https://x.com/uktaekook</t>
+  </si>
+  <si>
+    <t>https://bsky.app/profile/tktaekook.bsky.social</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=61568747848226</t>
+  </si>
+  <si>
+    <t>applemusic</t>
+  </si>
+  <si>
+    <t>tiktok</t>
+  </si>
+  <si>
+    <t>spotify</t>
   </si>
 </sst>
 </file>
@@ -2251,103 +2402,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2054D5E-E4FB-924C-9EF1-5CAB0A730ACC}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D3" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B4" t="s">
-        <v>479</v>
-      </c>
-      <c r="C4" t="s">
-        <v>458</v>
-      </c>
-      <c r="D4" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>489</v>
-      </c>
-      <c r="B5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D5" t="s">
-        <v>491</v>
-      </c>
-      <c r="E5" t="s">
-        <v>487</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3C3D97-69CD-0B46-9892-9CF02B5710A8}">
   <dimension ref="A1:N931"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -17680,7 +17734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B981EFC-1AD7-EC4B-9347-256C8C05A87B}">
   <dimension ref="A1:C177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19814,18 +19868,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB95BEF-80E6-B142-8CAB-761830DB341E}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>448</v>
@@ -19839,10 +19903,31 @@
       <c r="E1" s="1" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B2" t="s">
         <v>451</v>
@@ -19856,10 +19941,13 @@
       <c r="E2" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B3" t="s">
         <v>454</v>
@@ -19873,47 +19961,226 @@
       <c r="E3" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="G3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H3" t="s">
+        <v>534</v>
+      </c>
+      <c r="I3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D5" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>467</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" t="s">
         <v>456</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C7" t="s">
         <v>457</v>
       </c>
-      <c r="D4" t="s">
-        <v>459</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D7" t="s">
+        <v>507</v>
+      </c>
+      <c r="E7" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>468</v>
-      </c>
-      <c r="B5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C5" t="s">
-        <v>461</v>
-      </c>
-      <c r="D5" t="s">
-        <v>462</v>
-      </c>
-      <c r="E5" t="s">
-        <v>463</v>
+      <c r="F7" t="s">
+        <v>536</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C8" t="s">
+        <v>470</v>
+      </c>
+      <c r="D8" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C9" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" t="s">
+        <v>512</v>
+      </c>
+      <c r="D10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>499</v>
+      </c>
+      <c r="B11" t="s">
+        <v>521</v>
+      </c>
+      <c r="C11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D11" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>500</v>
+      </c>
+      <c r="B12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C12" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>501</v>
+      </c>
+      <c r="B13" t="s">
+        <v>523</v>
+      </c>
+      <c r="C13" t="s">
+        <v>515</v>
+      </c>
+      <c r="D13" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>502</v>
+      </c>
+      <c r="B14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C14" t="s">
+        <v>516</v>
+      </c>
+      <c r="D14" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>503</v>
+      </c>
+      <c r="B15" t="s">
+        <v>525</v>
+      </c>
+      <c r="C15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>505</v>
+      </c>
+      <c r="B16" t="s">
+        <v>526</v>
+      </c>
+      <c r="C16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{06773369-1014-CA44-9BC0-AE4B7C644AAC}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{24D47808-99B7-8040-8856-9D231F6314CE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45953261-3892-AF44-BD43-F53DBB4833E1}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19935,24 +20202,133 @@
         <v>419</v>
       </c>
       <c r="F1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B2" s="10">
         <v>45580</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D2" t="s">
         <v>440</v>
       </c>
       <c r="E2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2054D5E-E4FB-924C-9EF1-5CAB0A730ACC}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>472</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D4" t="s">
+        <v>482</v>
+      </c>
+      <c r="F4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" t="s">
+        <v>489</v>
+      </c>
+      <c r="D5" t="s">
+        <v>490</v>
+      </c>
+      <c r="E5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F5" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AFFEF4-B7C4-BE46-9AFD-CCE30CEB26F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1197A53C-E62F-D545-9C6B-789FEC51C5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15020" yWindow="3080" windowWidth="22560" windowHeight="17440" activeTab="5" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="560">
   <si>
     <t>Jungkook</t>
   </si>
@@ -1412,18 +1412,9 @@
     <t>streamfortaekook</t>
   </si>
   <si>
-    <t>streaming</t>
-  </si>
-  <si>
-    <t>fb for streaming</t>
-  </si>
-  <si>
     <t>tetekoofm</t>
   </si>
   <si>
-    <t>stationhead</t>
-  </si>
-  <si>
     <t>taekookuk</t>
   </si>
   <si>
@@ -1440,9 +1431,6 @@
   </si>
   <si>
     <t>Voting</t>
-  </si>
-  <si>
-    <t>fb for voting</t>
   </si>
   <si>
     <t>logo</t>
@@ -1681,6 +1669,72 @@
   </si>
   <si>
     <t>spotify</t>
+  </si>
+  <si>
+    <t>https://x.com/Taekook_india</t>
+  </si>
+  <si>
+    <t>https://x.com/TKvotingteam</t>
+  </si>
+  <si>
+    <t>https://x.com/TK_Mexico</t>
+  </si>
+  <si>
+    <t>https://x.com/_TKASIA</t>
+  </si>
+  <si>
+    <t>https://x.com/jp_taekook_</t>
+  </si>
+  <si>
+    <t>tkph.jpeg</t>
+  </si>
+  <si>
+    <t>tkphillipines</t>
+  </si>
+  <si>
+    <t>Phillipines</t>
+  </si>
+  <si>
+    <t>https://x.com/tk_philippines</t>
+  </si>
+  <si>
+    <t>https://x.com/taekook_IDN</t>
+  </si>
+  <si>
+    <t>https://x.com/TK_Colombia_</t>
+  </si>
+  <si>
+    <t>https://x.com/naver_taekook</t>
+  </si>
+  <si>
+    <t>https://x.com/TKTiktok_</t>
+  </si>
+  <si>
+    <t>https://x.com/TaekookEurope</t>
+  </si>
+  <si>
+    <t>https://x.com/TaeKook_USA</t>
+  </si>
+  <si>
+    <t>https://x.com/tk_honduras</t>
+  </si>
+  <si>
+    <t>https://x.com/Germany_Taekook</t>
+  </si>
+  <si>
+    <t>tknaver.jpeg</t>
+  </si>
+  <si>
+    <t>tknaver</t>
+  </si>
+  <si>
+    <t>Naver</t>
+  </si>
+  <si>
+    <t>Streaming</t>
+  </si>
+  <si>
+    <t>Stationhead</t>
   </si>
 </sst>
 </file>
@@ -19870,7 +19924,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB95BEF-80E6-B142-8CAB-761830DB341E}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -19889,7 +19943,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>448</v>
@@ -19904,124 +19958,124 @@
         <v>419</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B2" t="s">
         <v>451</v>
       </c>
       <c r="C2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E2" t="s">
-        <v>453</v>
+        <v>558</v>
       </c>
       <c r="F2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D3" t="s">
-        <v>455</v>
-      </c>
-      <c r="E3" t="s">
-        <v>453</v>
+        <v>559</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" t="s">
         <v>458</v>
       </c>
-      <c r="D4" t="s">
-        <v>461</v>
+      <c r="F4" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="B5" t="s">
-        <v>509</v>
+        <v>556</v>
       </c>
       <c r="C5" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D5" t="s">
-        <v>508</v>
+        <v>557</v>
+      </c>
+      <c r="F5" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="B6" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
       <c r="C6" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E6" t="s">
-        <v>462</v>
+        <v>504</v>
+      </c>
+      <c r="F6" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B7" t="s">
         <v>456</v>
@@ -20030,151 +20084,209 @@
         <v>457</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
-      </c>
-      <c r="E7" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F7" t="s">
-        <v>536</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="B8" t="s">
-        <v>506</v>
+        <v>453</v>
       </c>
       <c r="C8" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="D8" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F8" t="s">
+        <v>532</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="C9" t="s">
-        <v>511</v>
+        <v>466</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F9" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B10" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C10" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F10" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B11" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C11" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F11" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B12" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C12" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D12" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F12" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B13" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C13" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D13" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F13" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B14" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C14" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D14" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F14" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>498</v>
+      </c>
+      <c r="B15" t="s">
+        <v>520</v>
+      </c>
+      <c r="C15" t="s">
+        <v>512</v>
+      </c>
+      <c r="D15" t="s">
         <v>503</v>
       </c>
-      <c r="B15" t="s">
-        <v>525</v>
-      </c>
-      <c r="C15" t="s">
-        <v>517</v>
-      </c>
-      <c r="D15" t="s">
-        <v>507</v>
+      <c r="F15" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B16" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C16" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D16" t="s">
-        <v>507</v>
+        <v>503</v>
+      </c>
+      <c r="F16" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B17" t="s">
+        <v>522</v>
+      </c>
+      <c r="C17" t="s">
+        <v>514</v>
+      </c>
+      <c r="D17" t="s">
+        <v>503</v>
+      </c>
+      <c r="F17" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B18" t="s">
+        <v>544</v>
+      </c>
+      <c r="C18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D18" t="s">
+        <v>503</v>
+      </c>
+      <c r="F18" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1" xr:uid="{06773369-1014-CA44-9BC0-AE4B7C644AAC}"/>
-    <hyperlink ref="I7" r:id="rId2" xr:uid="{24D47808-99B7-8040-8856-9D231F6314CE}"/>
+    <hyperlink ref="I8" r:id="rId2" xr:uid="{24D47808-99B7-8040-8856-9D231F6314CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20202,24 +20314,24 @@
         <v>419</v>
       </c>
       <c r="F1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B2" s="10">
         <v>45580</v>
       </c>
       <c r="C2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D2" t="s">
         <v>440</v>
       </c>
       <c r="E2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -20242,19 +20354,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>449</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>419</v>
@@ -20262,73 +20374,73 @@
     </row>
     <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" t="s">
         <v>476</v>
       </c>
-      <c r="C2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D2" t="s">
-        <v>480</v>
-      </c>
       <c r="F2" s="9" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" t="s">
         <v>477</v>
       </c>
-      <c r="C3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D3" t="s">
-        <v>481</v>
-      </c>
       <c r="F3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" t="s">
         <v>478</v>
       </c>
-      <c r="C4" t="s">
-        <v>458</v>
-      </c>
-      <c r="D4" t="s">
-        <v>482</v>
-      </c>
       <c r="F4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B5" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D5" t="s">
+        <v>486</v>
+      </c>
+      <c r="E5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F5" t="s">
         <v>490</v>
-      </c>
-      <c r="E5" t="s">
-        <v>486</v>
-      </c>
-      <c r="F5" t="s">
-        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1197A53C-E62F-D545-9C6B-789FEC51C5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0358ADC-379E-5843-8029-DBEFEACB9C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="3080" windowWidth="22560" windowHeight="17440" activeTab="5" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
+    <workbookView xWindow="15020" yWindow="3080" windowWidth="22560" windowHeight="17440" activeTab="7" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
   <sheets>
     <sheet name="Upcoming" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="612">
   <si>
     <t>Jungkook</t>
   </si>
@@ -1472,12 +1472,6 @@
     <t>request_link</t>
   </si>
   <si>
-    <t>Hot106</t>
-  </si>
-  <si>
-    <t>Island106</t>
-  </si>
-  <si>
     <t>TuckA56Radio</t>
   </si>
   <si>
@@ -1735,13 +1729,175 @@
   </si>
   <si>
     <t>Stationhead</t>
+  </si>
+  <si>
+    <t>TaekookReport</t>
+  </si>
+  <si>
+    <t>https://x.com/TaekookReport</t>
+  </si>
+  <si>
+    <t>https://hot106.cgrmedia.ca/request</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/night-request-live-10009/</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/k-pop-radio-9003/</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/pop-1019-8470/</t>
+  </si>
+  <si>
+    <t>https://thezoo96.wixsite.com/thezooph/the-zoo-recent-songs</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/1027-kiis-fm-los-angeles-185/</t>
+  </si>
+  <si>
+    <t>https://www.iheart.com/live/z100-1469/</t>
+  </si>
+  <si>
+    <t>https://tofupopradio.teroradio.com/</t>
+  </si>
+  <si>
+    <t>https://bigbradio.net/kpop</t>
+  </si>
+  <si>
+    <t>https://ecaradio.org/</t>
+  </si>
+  <si>
+    <t>https://valleyfreeradio.org/listen/</t>
+  </si>
+  <si>
+    <t>https://onlyhit.us/en/listen/</t>
+  </si>
+  <si>
+    <t>http://listen.5fm.co.za/listen5fm/#listenLiveTab</t>
+  </si>
+  <si>
+    <t>nightrequestlive.jpeg</t>
+  </si>
+  <si>
+    <t>kpopradio.jpeg</t>
+  </si>
+  <si>
+    <t>pop101_9.jpeg</t>
+  </si>
+  <si>
+    <t>kiisfm102_7.jpeg</t>
+  </si>
+  <si>
+    <t>z100ny.jpeg</t>
+  </si>
+  <si>
+    <t>thezoo.jpeg</t>
+  </si>
+  <si>
+    <t>tofupop.jpeg</t>
+  </si>
+  <si>
+    <t>eca.jpeg</t>
+  </si>
+  <si>
+    <t>valleyfree.jpeg</t>
+  </si>
+  <si>
+    <t>onlyhit.jpeg</t>
+  </si>
+  <si>
+    <t>5fm.jpeg</t>
+  </si>
+  <si>
+    <t>bigbradio.jpeg</t>
+  </si>
+  <si>
+    <t>Hot 106</t>
+  </si>
+  <si>
+    <t>Island 106</t>
+  </si>
+  <si>
+    <t>Night Request Live</t>
+  </si>
+  <si>
+    <t>Kpop Radio</t>
+  </si>
+  <si>
+    <t>Pop 101.9</t>
+  </si>
+  <si>
+    <t>KIIS FM 102.7</t>
+  </si>
+  <si>
+    <t>Z100NY</t>
+  </si>
+  <si>
+    <t>The Zoo and Lite Rock Manila</t>
+  </si>
+  <si>
+    <t>Tofu Pop Radio</t>
+  </si>
+  <si>
+    <t>Big B Radio</t>
+  </si>
+  <si>
+    <t>ECA</t>
+  </si>
+  <si>
+    <t>Only Hit</t>
+  </si>
+  <si>
+    <t>5 FM</t>
+  </si>
+  <si>
+    <t>https://island106.com/</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>https://ecaradio2.weebly.com/song-requests.html</t>
+  </si>
+  <si>
+    <t>https://onlyhit.us/en/contact/</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSe1yaIX9vTlkW8uVFqkF4ElCrsJ4R131b5lOQx7PlmwzYIaPg/viewform</t>
+  </si>
+  <si>
+    <t>OK Asia</t>
+  </si>
+  <si>
+    <t>NewYork</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>bossglobalradio.jpeg</t>
+  </si>
+  <si>
+    <t>Boss Global Radio</t>
+  </si>
+  <si>
+    <t>https://www.bossglobalradio.com/</t>
+  </si>
+  <si>
+    <t>https://www.bossglobalradio.com/request</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1785,6 +1941,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF71767B"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1807,7 +1969,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1821,6 +1983,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -19924,7 +20087,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB95BEF-80E6-B142-8CAB-761830DB341E}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -19958,25 +20121,25 @@
         <v>419</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -19990,10 +20153,10 @@
         <v>455</v>
       </c>
       <c r="D2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -20007,27 +20170,27 @@
         <v>455</v>
       </c>
       <c r="D3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F3" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="G3" t="s">
+        <v>527</v>
+      </c>
+      <c r="H3" t="s">
         <v>528</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>529</v>
-      </c>
-      <c r="H3" t="s">
-        <v>530</v>
-      </c>
-      <c r="I3" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C4" t="s">
         <v>455</v>
@@ -20036,41 +20199,41 @@
         <v>458</v>
       </c>
       <c r="F4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C5" t="s">
         <v>455</v>
       </c>
       <c r="D5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C6" t="s">
         <v>455</v>
       </c>
       <c r="D6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -20087,7 +20250,7 @@
         <v>458</v>
       </c>
       <c r="F7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -20101,186 +20264,194 @@
         <v>454</v>
       </c>
       <c r="D8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F8" t="s">
+        <v>530</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>534</v>
-      </c>
       <c r="I8" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C9" t="s">
         <v>466</v>
       </c>
       <c r="D9" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D10" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F11" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B12" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F12" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F13" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C14" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F14" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D15" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D16" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F16" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>499</v>
+      </c>
+      <c r="B17" t="s">
+        <v>520</v>
+      </c>
+      <c r="C17" t="s">
+        <v>512</v>
+      </c>
+      <c r="D17" t="s">
         <v>501</v>
       </c>
-      <c r="B17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C17" t="s">
-        <v>514</v>
-      </c>
-      <c r="D17" t="s">
-        <v>503</v>
-      </c>
       <c r="F17" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B18" t="s">
+        <v>542</v>
+      </c>
+      <c r="C18" t="s">
         <v>543</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>501</v>
+      </c>
+      <c r="F18" t="s">
         <v>544</v>
       </c>
-      <c r="C18" t="s">
-        <v>545</v>
-      </c>
-      <c r="D18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F18" t="s">
-        <v>546</v>
+    </row>
+    <row r="19" spans="1:6" ht="19" x14ac:dyDescent="0.2">
+      <c r="B19" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="F19" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -20341,13 +20512,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2054D5E-E4FB-924C-9EF1-5CAB0A730ACC}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -20374,76 +20545,282 @@
     </row>
     <row r="2" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s">
-        <v>472</v>
+        <v>585</v>
       </c>
       <c r="C2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>474</v>
+      </c>
+      <c r="E2" t="s">
+        <v>560</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B3" t="s">
-        <v>473</v>
+        <v>586</v>
       </c>
       <c r="C3" t="s">
-        <v>455</v>
+        <v>599</v>
       </c>
       <c r="D3" t="s">
-        <v>477</v>
+        <v>475</v>
+      </c>
+      <c r="E3" t="s">
+        <v>598</v>
       </c>
       <c r="F3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C4" t="s">
         <v>455</v>
       </c>
       <c r="D4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D5" t="s">
+        <v>569</v>
+      </c>
+      <c r="E5" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" t="s">
+        <v>610</v>
+      </c>
+      <c r="E6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>482</v>
+      </c>
+      <c r="B7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D7" t="s">
         <v>484</v>
       </c>
-      <c r="B5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C5" t="s">
-        <v>485</v>
-      </c>
-      <c r="D5" t="s">
-        <v>486</v>
-      </c>
-      <c r="E5" t="s">
-        <v>482</v>
-      </c>
-      <c r="F5" t="s">
-        <v>490</v>
+      <c r="E7" t="s">
+        <v>480</v>
+      </c>
+      <c r="F7" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C8" t="s">
+        <v>607</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C9" t="s">
+        <v>607</v>
+      </c>
+      <c r="D9" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>589</v>
+      </c>
+      <c r="C10" t="s">
+        <v>607</v>
+      </c>
+      <c r="D10" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>576</v>
+      </c>
+      <c r="B11" t="s">
+        <v>590</v>
+      </c>
+      <c r="C11" t="s">
+        <v>601</v>
+      </c>
+      <c r="D11" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>577</v>
+      </c>
+      <c r="B12" t="s">
+        <v>591</v>
+      </c>
+      <c r="C12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>578</v>
+      </c>
+      <c r="B13" t="s">
+        <v>592</v>
+      </c>
+      <c r="C13" t="s">
+        <v>600</v>
+      </c>
+      <c r="D13" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>579</v>
+      </c>
+      <c r="B14" t="s">
+        <v>593</v>
+      </c>
+      <c r="C14" t="s">
+        <v>505</v>
+      </c>
+      <c r="D14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>584</v>
+      </c>
+      <c r="B15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C15" t="s">
+        <v>505</v>
+      </c>
+      <c r="D15" t="s">
+        <v>568</v>
+      </c>
+      <c r="E15" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>581</v>
+      </c>
+      <c r="B16" t="s">
+        <v>605</v>
+      </c>
+      <c r="C16" t="s">
+        <v>505</v>
+      </c>
+      <c r="D16" t="s">
+        <v>570</v>
+      </c>
+      <c r="E16" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>582</v>
+      </c>
+      <c r="B17" t="s">
+        <v>596</v>
+      </c>
+      <c r="C17" t="s">
+        <v>505</v>
+      </c>
+      <c r="D17" t="s">
+        <v>571</v>
+      </c>
+      <c r="E17" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>583</v>
+      </c>
+      <c r="B18" t="s">
+        <v>597</v>
+      </c>
+      <c r="C18" t="s">
+        <v>455</v>
+      </c>
+      <c r="D18" t="s">
+        <v>572</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D8" r:id="rId1" xr:uid="{9CF47BBB-6D4F-EF42-87AC-2620CBBA3A97}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/taekook_universe.xlsx
+++ b/taekook_universe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haripriyakrishnan/Downloads/Python/taekook_universe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0358ADC-379E-5843-8029-DBEFEACB9C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3045E0-09B7-A847-B00D-B9A27A83A502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15020" yWindow="3080" windowWidth="22560" windowHeight="17440" activeTab="7" xr2:uid="{52A6CF0C-9FDF-6A4B-B1CC-CBEE960F6C98}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="612">
   <si>
     <t>Jungkook</t>
   </si>
@@ -20596,6 +20596,9 @@
       <c r="D4" t="s">
         <v>476</v>
       </c>
+      <c r="E4" t="s">
+        <v>476</v>
+      </c>
       <c r="F4" t="s">
         <v>487</v>
       </c>
